--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4396" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4416" uniqueCount="406">
   <si>
     <t>Property</t>
   </si>
@@ -271,8 +271,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -502,6 +502,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Bundle.meta.tag</t>
   </si>
   <si>
@@ -583,6 +593,12 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -716,6 +732,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -723,6 +742,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -744,8 +766,8 @@
     <t>Die Aufgabe und das QES signierte Bundle.</t>
   </si>
   <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -794,6 +816,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -803,8 +828,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -860,8 +885,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -915,6 +940,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -942,8 +970,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1615,8 +1643,8 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="22.78515625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2975,16 +3003,16 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2995,10 +3023,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3024,13 +3052,13 @@
         <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3056,13 +3084,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3080,7 +3108,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3089,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3109,10 +3137,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3138,13 +3166,13 @@
         <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3194,7 +3222,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3223,10 +3251,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3249,16 +3277,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3284,13 +3312,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3308,7 +3336,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3337,10 +3365,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3363,16 +3391,16 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3422,7 +3450,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3431,30 +3459,30 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3477,16 +3505,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3494,7 +3522,7 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>78</v>
@@ -3512,31 +3540,31 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>88</v>
@@ -3560,15 +3588,15 @@
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3594,13 +3622,13 @@
         <v>124</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3650,7 +3678,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3671,18 +3699,18 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3705,16 +3733,16 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3764,7 +3792,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3773,7 +3801,7 @@
         <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>100</v>
@@ -3793,10 +3821,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3819,16 +3847,16 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3878,7 +3906,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3887,7 +3915,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>100</v>
@@ -3896,7 +3924,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3907,10 +3935,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4019,10 +4047,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4092,16 +4120,16 @@
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>116</v>
@@ -4133,14 +4161,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4162,16 +4190,16 @@
         <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4220,7 +4248,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4249,10 +4277,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4278,12 +4306,14 @@
         <v>102</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4332,7 +4362,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>88</v>
@@ -4361,10 +4391,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4390,12 +4420,14 @@
         <v>130</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4444,7 +4476,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>88</v>
@@ -4473,10 +4505,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4484,10 +4516,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4499,13 +4531,13 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4544,10 +4576,10 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
@@ -4556,7 +4588,7 @@
         <v>142</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4565,16 +4597,16 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4585,10 +4617,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4697,10 +4729,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4770,16 +4802,16 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>116</v>
@@ -4811,14 +4843,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4840,16 +4872,16 @@
         <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4898,7 +4930,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4927,10 +4959,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4956,10 +4988,10 @@
         <v>78</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5010,7 +5042,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5022,7 +5054,7 @@
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -5039,10 +5071,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5068,13 +5100,13 @@
         <v>130</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5124,7 +5156,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5153,10 +5185,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5179,13 +5211,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5236,7 +5268,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5254,7 +5286,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5265,10 +5297,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5291,13 +5323,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5348,7 +5380,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5357,7 +5389,7 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>100</v>
@@ -5366,7 +5398,7 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -5377,10 +5409,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5489,10 +5521,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5562,16 +5594,16 @@
         <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>116</v>
@@ -5603,14 +5635,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5632,16 +5664,16 @@
         <v>109</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5690,7 +5722,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5719,10 +5751,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5745,16 +5777,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5780,13 +5812,13 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -5804,7 +5836,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5833,10 +5865,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5859,16 +5891,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5918,7 +5950,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5947,10 +5979,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5973,13 +6005,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6030,7 +6062,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6039,7 +6071,7 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>100</v>
@@ -6048,7 +6080,7 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6059,10 +6091,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6171,10 +6203,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6244,16 +6276,16 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>116</v>
@@ -6285,14 +6317,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6314,16 +6346,16 @@
         <v>109</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6372,7 +6404,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6401,10 +6433,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6427,13 +6459,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6460,13 +6492,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -6484,7 +6516,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>88</v>
@@ -6513,10 +6545,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6542,13 +6574,13 @@
         <v>130</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6598,7 +6630,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6627,10 +6659,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6656,12 +6688,14 @@
         <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6710,7 +6744,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6739,10 +6773,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6768,12 +6802,14 @@
         <v>124</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -6822,7 +6858,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6851,10 +6887,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6880,12 +6916,14 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -6934,7 +6972,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6963,10 +7001,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6992,12 +7030,14 @@
         <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7046,7 +7086,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7075,10 +7115,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7101,13 +7141,13 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7158,7 +7198,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7167,7 +7207,7 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>100</v>
@@ -7176,7 +7216,7 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7187,10 +7227,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7299,10 +7339,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7372,16 +7412,16 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>116</v>
@@ -7413,14 +7453,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7442,16 +7482,16 @@
         <v>109</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7500,7 +7540,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7529,10 +7569,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7558,12 +7598,14 @@
         <v>102</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7612,7 +7654,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>88</v>
@@ -7641,10 +7683,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7670,12 +7712,14 @@
         <v>130</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -7724,7 +7768,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7753,10 +7797,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7782,13 +7826,13 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7838,7 +7882,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7867,10 +7911,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7896,13 +7940,13 @@
         <v>124</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7952,7 +7996,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -7981,10 +8025,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8007,16 +8051,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8066,7 +8110,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8084,7 +8128,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8095,13 +8139,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
@@ -8123,13 +8167,13 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8180,7 +8224,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8189,16 +8233,16 @@
         <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8209,10 +8253,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8321,10 +8365,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8394,16 +8438,16 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>116</v>
@@ -8435,14 +8479,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8464,16 +8508,16 @@
         <v>109</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -8522,7 +8566,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8551,10 +8595,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8580,10 +8624,10 @@
         <v>81</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8634,7 +8678,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8646,7 +8690,7 @@
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -8663,10 +8707,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8692,13 +8736,13 @@
         <v>130</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8748,7 +8792,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8777,10 +8821,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8803,13 +8847,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8860,7 +8904,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -8878,7 +8922,7 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -8889,10 +8933,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8915,13 +8959,13 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8972,7 +9016,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -8981,7 +9025,7 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>100</v>
@@ -8990,7 +9034,7 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9001,10 +9045,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9113,10 +9157,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9186,16 +9230,16 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>116</v>
@@ -9227,14 +9271,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9256,16 +9300,16 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9314,7 +9358,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9343,10 +9387,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9369,16 +9413,16 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9404,13 +9448,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9428,7 +9472,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9457,10 +9501,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9483,16 +9527,16 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9542,7 +9586,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9571,10 +9615,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9597,13 +9641,13 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9654,7 +9698,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9663,7 +9707,7 @@
         <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>100</v>
@@ -9672,7 +9716,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -9683,10 +9727,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9795,10 +9839,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9868,16 +9912,16 @@
         <v>78</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>116</v>
@@ -9909,14 +9953,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9938,16 +9982,16 @@
         <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -9996,7 +10040,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10025,10 +10069,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10051,13 +10095,13 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10084,13 +10128,13 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10108,7 +10152,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>88</v>
@@ -10137,10 +10181,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10166,13 +10210,13 @@
         <v>130</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10222,7 +10266,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -10251,10 +10295,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10280,12 +10324,14 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10334,7 +10380,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10363,10 +10409,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10392,12 +10438,14 @@
         <v>124</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -10446,7 +10494,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10475,10 +10523,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10504,12 +10552,14 @@
         <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -10558,7 +10608,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10587,10 +10637,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10616,12 +10666,14 @@
         <v>102</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -10670,7 +10722,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -10699,10 +10751,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10725,13 +10777,13 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10782,7 +10834,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -10791,7 +10843,7 @@
         <v>88</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>100</v>
@@ -10800,7 +10852,7 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -10811,10 +10863,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10923,10 +10975,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10996,16 +11048,16 @@
         <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>116</v>
@@ -11037,14 +11089,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11066,16 +11118,16 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11124,7 +11176,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11153,10 +11205,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11182,12 +11234,14 @@
         <v>102</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -11236,7 +11290,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>88</v>
@@ -11265,10 +11319,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11294,12 +11348,14 @@
         <v>130</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -11348,7 +11404,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11377,10 +11433,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11406,13 +11462,13 @@
         <v>102</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11462,7 +11518,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -11491,10 +11547,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11520,13 +11576,13 @@
         <v>124</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11576,7 +11632,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -11605,10 +11661,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11631,16 +11687,16 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11690,7 +11746,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -11708,7 +11764,7 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -11719,13 +11775,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -11747,13 +11803,13 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11804,7 +11860,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -11813,16 +11869,16 @@
         <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -11833,10 +11889,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11945,10 +12001,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12018,16 +12074,16 @@
         <v>78</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>116</v>
@@ -12059,14 +12115,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12088,16 +12144,16 @@
         <v>109</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12146,7 +12202,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12175,10 +12231,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12204,10 +12260,10 @@
         <v>81</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12258,7 +12314,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12270,7 +12326,7 @@
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
@@ -12287,10 +12343,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12316,13 +12372,13 @@
         <v>130</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12372,7 +12428,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12401,10 +12457,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12427,16 +12483,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12486,7 +12542,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -12504,7 +12560,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -12515,10 +12571,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12541,13 +12597,13 @@
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12598,7 +12654,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -12607,7 +12663,7 @@
         <v>88</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>100</v>
@@ -12616,7 +12672,7 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -12627,10 +12683,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12739,10 +12795,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12812,16 +12868,16 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>116</v>
@@ -12853,14 +12909,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -12882,16 +12938,16 @@
         <v>109</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -12940,7 +12996,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -12969,10 +13025,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12995,16 +13051,16 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13030,13 +13086,13 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -13054,7 +13110,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13083,10 +13139,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13109,16 +13165,16 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13168,7 +13224,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13197,10 +13253,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13223,13 +13279,13 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13280,7 +13336,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13289,7 +13345,7 @@
         <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>100</v>
@@ -13298,7 +13354,7 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -13309,10 +13365,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13421,10 +13477,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13494,16 +13550,16 @@
         <v>78</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>116</v>
@@ -13535,14 +13591,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13564,16 +13620,16 @@
         <v>109</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -13622,7 +13678,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -13651,10 +13707,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13677,13 +13733,13 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13710,13 +13766,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -13734,7 +13790,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>88</v>
@@ -13763,10 +13819,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13792,13 +13848,13 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13848,7 +13904,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -13877,10 +13933,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13906,12 +13962,14 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -13960,7 +14018,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -13989,10 +14047,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14018,12 +14076,14 @@
         <v>124</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14072,7 +14132,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14101,10 +14161,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14130,12 +14190,14 @@
         <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -14184,7 +14246,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14213,10 +14275,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14242,12 +14304,14 @@
         <v>102</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -14296,7 +14360,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -14325,10 +14389,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14351,13 +14415,13 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14408,7 +14472,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -14417,7 +14481,7 @@
         <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>100</v>
@@ -14426,7 +14490,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -14437,10 +14501,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14549,10 +14613,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14622,16 +14686,16 @@
         <v>78</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF115" t="s" s="2">
         <v>116</v>
@@ -14663,14 +14727,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -14692,16 +14756,16 @@
         <v>109</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -14750,7 +14814,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -14779,10 +14843,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14808,12 +14872,14 @@
         <v>102</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -14862,7 +14928,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>88</v>
@@ -14891,10 +14957,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14920,12 +14986,14 @@
         <v>130</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>78</v>
@@ -14974,7 +15042,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -15003,10 +15071,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15032,13 +15100,13 @@
         <v>102</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15088,7 +15156,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15117,10 +15185,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15146,13 +15214,13 @@
         <v>124</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15202,7 +15270,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15231,10 +15299,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15257,16 +15325,16 @@
         <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -15316,7 +15384,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -15334,7 +15402,7 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -15345,10 +15413,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15371,19 +15439,19 @@
         <v>89</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -15432,7 +15500,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -15441,7 +15509,7 @@
         <v>88</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>100</v>
@@ -15450,7 +15518,7 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>

--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
